--- a/import/data_import/Aggression/PublicnEUro_record_Aggression.xlsx
+++ b/import/data_import/Aggression/PublicnEUro_record_Aggression.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\vincentajoubi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\cyrilpernet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5633C051-77E9-428E-887D-201F521006B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51765DB5-45D8-4B86-8511-77A9635F9E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dataset_info" sheetId="1" r:id="rId1"/>
@@ -21,10 +21,20 @@
     <sheet name="funding" sheetId="4" r:id="rId6"/>
     <sheet name="publications" sheetId="5" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="hjfek71Zy+vJ/dydEKhFRDpjahq2hqu6IM6M7MYdjxs="/>
@@ -327,7 +337,7 @@
     <t>https:/doi.org/10.1016/j.jpsychires.2017.05.003</t>
   </si>
   <si>
-    <t>https://doi.org/10.70883/XXXX</t>
+    <t>https://doi.org/10.70883/KMPE3139</t>
   </si>
 </sst>
 </file>
